--- a/results/04_final_refined_daily_hydroclimate_data/904/Daily_temperature_and_precipitation_station_904.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/904/Daily_temperature_and_precipitation_station_904.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>Year</t>
   </si>
@@ -514,19 +514,16 @@
         <v>1</v>
       </c>
       <c r="D2">
-        <v>27.8</v>
+        <v>28.2</v>
       </c>
       <c r="E2">
-        <v>18.2</v>
+        <v>17.5</v>
       </c>
       <c r="F2">
         <v>23</v>
       </c>
-      <c r="I2">
-        <v>27.8</v>
-      </c>
-      <c r="L2">
-        <v>17.9</v>
+      <c r="G2">
+        <v>18.6</v>
       </c>
       <c r="R2" s="2">
         <v>26512</v>
@@ -557,14 +554,14 @@
       <c r="F3">
         <v>23</v>
       </c>
-      <c r="I3">
-        <v>28.4</v>
-      </c>
-      <c r="L3">
-        <v>21.6</v>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>24.8</v>
       </c>
       <c r="M3">
-        <v>18.6</v>
+        <v>15.7</v>
       </c>
       <c r="R3" s="2">
         <v>26513</v>
@@ -586,24 +583,21 @@
       <c r="C4">
         <v>3</v>
       </c>
+      <c r="D4">
+        <v>28.6</v>
+      </c>
       <c r="E4">
         <v>17.8</v>
       </c>
-      <c r="H4">
-        <v>18.4</v>
-      </c>
-      <c r="I4">
-        <v>28.6</v>
+      <c r="F4">
+        <v>23.2</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
       </c>
       <c r="J4">
         <v>24.6</v>
       </c>
-      <c r="K4">
-        <v>16</v>
-      </c>
-      <c r="L4">
-        <v>21.8</v>
-      </c>
       <c r="M4">
         <v>18.1</v>
       </c>
@@ -636,11 +630,11 @@
       <c r="F5">
         <v>24.1</v>
       </c>
-      <c r="I5">
-        <v>30.4</v>
-      </c>
-      <c r="L5">
-        <v>20.6</v>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>25.8</v>
       </c>
       <c r="M5">
         <v>19.6</v>
@@ -665,14 +659,23 @@
       <c r="C6">
         <v>5</v>
       </c>
-      <c r="I6">
-        <v>30.6</v>
-      </c>
-      <c r="L6">
-        <v>21.2</v>
+      <c r="D6">
+        <v>29.9</v>
+      </c>
+      <c r="E6">
+        <v>17.3</v>
+      </c>
+      <c r="F6">
+        <v>23.59</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>26.2</v>
       </c>
       <c r="M6">
-        <v>19.4</v>
+        <v>19.8</v>
       </c>
       <c r="R6" s="2">
         <v>26516</v>
@@ -694,6 +697,21 @@
       <c r="C7">
         <v>6</v>
       </c>
+      <c r="D7">
+        <v>28.4</v>
+      </c>
+      <c r="E7">
+        <v>16.8</v>
+      </c>
+      <c r="F7">
+        <v>22.6</v>
+      </c>
+      <c r="H7">
+        <v>18.4</v>
+      </c>
+      <c r="K7">
+        <v>18.2</v>
+      </c>
       <c r="L7">
         <v>20</v>
       </c>
@@ -726,15 +744,15 @@
       <c r="F8">
         <v>23.1</v>
       </c>
-      <c r="J8">
-        <v>25.6</v>
+      <c r="H8">
+        <v>18.6</v>
+      </c>
+      <c r="K8">
+        <v>17.4</v>
       </c>
       <c r="L8">
         <v>21.6</v>
       </c>
-      <c r="M8">
-        <v>19.8</v>
-      </c>
       <c r="R8" s="2">
         <v>26518</v>
       </c>
@@ -764,15 +782,15 @@
       <c r="F9">
         <v>21.6</v>
       </c>
-      <c r="J9">
-        <v>25.6</v>
+      <c r="H9">
+        <v>17.6</v>
+      </c>
+      <c r="K9">
+        <v>15.8</v>
       </c>
       <c r="L9">
         <v>19.9</v>
       </c>
-      <c r="M9">
-        <v>19.8</v>
-      </c>
       <c r="R9" s="2">
         <v>26519</v>
       </c>
@@ -802,14 +820,14 @@
       <c r="F10">
         <v>23.3</v>
       </c>
-      <c r="J10">
-        <v>22.6</v>
+      <c r="H10">
+        <v>19.8</v>
+      </c>
+      <c r="K10">
+        <v>16.8</v>
       </c>
       <c r="L10">
-        <v>19.9</v>
-      </c>
-      <c r="M10">
-        <v>17.4</v>
+        <v>19.4</v>
       </c>
       <c r="R10" s="2">
         <v>26520</v>
@@ -840,15 +858,15 @@
       <c r="F11">
         <v>23.3</v>
       </c>
-      <c r="J11">
-        <v>25.4</v>
+      <c r="H11">
+        <v>18.6</v>
+      </c>
+      <c r="K11">
+        <v>15.9</v>
       </c>
       <c r="L11">
         <v>21.2</v>
       </c>
-      <c r="M11">
-        <v>18.8</v>
-      </c>
       <c r="R11" s="2">
         <v>26521</v>
       </c>
@@ -869,18 +887,18 @@
       <c r="C12">
         <v>11</v>
       </c>
-      <c r="I12">
-        <v>30.4</v>
+      <c r="D12">
+        <v>30.3</v>
+      </c>
+      <c r="E12">
+        <v>17.9</v>
+      </c>
+      <c r="F12">
+        <v>24.1</v>
       </c>
       <c r="K12">
         <v>16.2</v>
       </c>
-      <c r="L12">
-        <v>18.4</v>
-      </c>
-      <c r="M12">
-        <v>20.2</v>
-      </c>
       <c r="R12" s="2">
         <v>26522</v>
       </c>
@@ -902,7 +920,7 @@
         <v>12</v>
       </c>
       <c r="D13">
-        <v>29.8</v>
+        <v>29.6</v>
       </c>
       <c r="E13">
         <v>17.8</v>
@@ -910,11 +928,14 @@
       <c r="F13">
         <v>23.7</v>
       </c>
+      <c r="I13">
+        <v>29.6</v>
+      </c>
       <c r="K13">
         <v>17.2</v>
       </c>
-      <c r="M13">
-        <v>19.8</v>
+      <c r="L13">
+        <v>17</v>
       </c>
       <c r="R13" s="2">
         <v>26523</v>
@@ -945,11 +966,14 @@
       <c r="F14">
         <v>24.4</v>
       </c>
+      <c r="I14">
+        <v>30.6</v>
+      </c>
       <c r="K14">
         <v>17.4</v>
       </c>
-      <c r="M14">
-        <v>20.2</v>
+      <c r="L14">
+        <v>18.2</v>
       </c>
       <c r="R14" s="2">
         <v>26524</v>
@@ -971,12 +995,18 @@
       <c r="C15">
         <v>14</v>
       </c>
+      <c r="D15">
+        <v>26.6</v>
+      </c>
+      <c r="E15">
+        <v>18</v>
+      </c>
+      <c r="F15">
+        <v>22.3</v>
+      </c>
       <c r="K15">
         <v>17.4</v>
       </c>
-      <c r="M15">
-        <v>18.6</v>
-      </c>
       <c r="R15" s="2">
         <v>26525</v>
       </c>
@@ -997,11 +1027,23 @@
       <c r="C16">
         <v>15</v>
       </c>
+      <c r="D16">
+        <v>28.4</v>
+      </c>
+      <c r="E16">
+        <v>17.6</v>
+      </c>
+      <c r="F16">
+        <v>23</v>
+      </c>
+      <c r="I16">
+        <v>23.2</v>
+      </c>
       <c r="K16">
         <v>16.8</v>
       </c>
-      <c r="M16">
-        <v>16.8</v>
+      <c r="L16">
+        <v>17.1</v>
       </c>
       <c r="R16" s="2">
         <v>26526</v>
@@ -1023,12 +1065,18 @@
       <c r="C17">
         <v>16</v>
       </c>
+      <c r="D17">
+        <v>22.8</v>
+      </c>
+      <c r="E17">
+        <v>16</v>
+      </c>
+      <c r="F17">
+        <v>19.4</v>
+      </c>
       <c r="L17">
         <v>19.4</v>
       </c>
-      <c r="M17">
-        <v>18.4</v>
-      </c>
       <c r="R17" s="2">
         <v>26527</v>
       </c>
@@ -1049,12 +1097,18 @@
       <c r="C18">
         <v>17</v>
       </c>
+      <c r="D18">
+        <v>28.8</v>
+      </c>
+      <c r="E18">
+        <v>17.2</v>
+      </c>
+      <c r="F18">
+        <v>23</v>
+      </c>
       <c r="L18">
         <v>21.2</v>
       </c>
-      <c r="M18">
-        <v>18.6</v>
-      </c>
       <c r="R18" s="2">
         <v>26528</v>
       </c>
@@ -1075,11 +1129,20 @@
       <c r="C19">
         <v>18</v>
       </c>
+      <c r="D19">
+        <v>27.4</v>
+      </c>
+      <c r="E19">
+        <v>18.2</v>
+      </c>
+      <c r="F19">
+        <v>22.8</v>
+      </c>
+      <c r="I19">
+        <v>27.4</v>
+      </c>
       <c r="L19">
-        <v>20.8</v>
-      </c>
-      <c r="M19">
-        <v>19.8</v>
+        <v>18.1</v>
       </c>
       <c r="R19" s="2">
         <v>26529</v>
@@ -1101,15 +1164,27 @@
       <c r="C20">
         <v>19</v>
       </c>
+      <c r="D20">
+        <v>27.4</v>
+      </c>
+      <c r="E20">
+        <v>18.2</v>
+      </c>
+      <c r="F20">
+        <v>22.8</v>
+      </c>
+      <c r="H20">
+        <v>18.4</v>
+      </c>
       <c r="I20">
         <v>27.4</v>
       </c>
+      <c r="K20">
+        <v>15.7</v>
+      </c>
       <c r="L20">
         <v>18.1</v>
       </c>
-      <c r="M20">
-        <v>19.8</v>
-      </c>
       <c r="R20" s="2">
         <v>26530</v>
       </c>
@@ -1134,22 +1209,22 @@
         <v>26.8</v>
       </c>
       <c r="E21">
-        <v>17.4</v>
+        <v>15.9</v>
       </c>
       <c r="F21">
-        <v>22.1</v>
+        <v>21.4</v>
       </c>
       <c r="H21">
         <v>18.6</v>
       </c>
+      <c r="I21">
+        <v>25.6</v>
+      </c>
       <c r="K21">
         <v>16.8</v>
       </c>
       <c r="L21">
-        <v>19.8</v>
-      </c>
-      <c r="M21">
-        <v>19</v>
+        <v>17.2</v>
       </c>
       <c r="R21" s="2">
         <v>26531</v>
@@ -1171,17 +1246,17 @@
       <c r="C22">
         <v>21</v>
       </c>
+      <c r="D22">
+        <v>26.2</v>
+      </c>
+      <c r="F22">
+        <v>19.9</v>
+      </c>
       <c r="H22">
         <v>18.4</v>
       </c>
-      <c r="J22">
-        <v>22.6</v>
-      </c>
-      <c r="L22">
-        <v>19.8</v>
-      </c>
-      <c r="M22">
-        <v>18.8</v>
+      <c r="O22" t="s">
+        <v>20</v>
       </c>
       <c r="R22" s="2">
         <v>26532</v>
@@ -1203,20 +1278,23 @@
       <c r="C23">
         <v>22</v>
       </c>
+      <c r="D23">
+        <v>26.6</v>
+      </c>
+      <c r="E23">
+        <v>17.2</v>
+      </c>
+      <c r="F23">
+        <v>21.9</v>
+      </c>
       <c r="H23">
         <v>17.4</v>
       </c>
-      <c r="I23">
-        <v>26.6</v>
-      </c>
       <c r="J23">
         <v>21.8</v>
       </c>
-      <c r="L23">
-        <v>17.1</v>
-      </c>
-      <c r="M23">
-        <v>18.6</v>
+      <c r="K23">
+        <v>14.7</v>
       </c>
       <c r="R23" s="2">
         <v>26533</v>
@@ -1241,18 +1319,9 @@
       <c r="H24">
         <v>18.4</v>
       </c>
-      <c r="I24">
-        <v>28.2</v>
-      </c>
       <c r="J24">
         <v>24.6</v>
       </c>
-      <c r="L24">
-        <v>19</v>
-      </c>
-      <c r="M24">
-        <v>20</v>
-      </c>
       <c r="R24" s="2">
         <v>26534</v>
       </c>
@@ -1273,30 +1342,12 @@
       <c r="C25">
         <v>24</v>
       </c>
-      <c r="D25">
-        <v>28.6</v>
-      </c>
-      <c r="E25">
-        <v>17.8</v>
-      </c>
-      <c r="F25">
-        <v>23.2</v>
-      </c>
       <c r="H25">
-        <v>17.6</v>
-      </c>
-      <c r="I25">
-        <v>24.3</v>
+        <v>17.9</v>
       </c>
       <c r="J25">
         <v>20.4</v>
       </c>
-      <c r="L25">
-        <v>16.6</v>
-      </c>
-      <c r="M25">
-        <v>18.8</v>
-      </c>
       <c r="R25" s="2">
         <v>26535</v>
       </c>
@@ -1317,8 +1368,17 @@
       <c r="C26">
         <v>25</v>
       </c>
+      <c r="D26">
+        <v>28.6</v>
+      </c>
+      <c r="E26">
+        <v>17.8</v>
+      </c>
+      <c r="F26">
+        <v>23.2</v>
+      </c>
       <c r="H26">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="J26">
         <v>20.4</v>
@@ -1326,18 +1386,6 @@
       <c r="K26">
         <v>16.5</v>
       </c>
-      <c r="L26">
-        <v>21.8</v>
-      </c>
-      <c r="M26">
-        <v>18.8</v>
-      </c>
-      <c r="N26" t="s">
-        <v>20</v>
-      </c>
-      <c r="P26" t="s">
-        <v>20</v>
-      </c>
       <c r="R26" s="2">
         <v>26536</v>
       </c>
@@ -1358,20 +1406,11 @@
       <c r="C27">
         <v>26</v>
       </c>
-      <c r="D27">
-        <v>26.6</v>
-      </c>
-      <c r="E27">
-        <v>18.6</v>
-      </c>
-      <c r="F27">
-        <v>22.6</v>
-      </c>
       <c r="H27">
         <v>19.4</v>
       </c>
-      <c r="J27">
-        <v>23.9</v>
+      <c r="M27">
+        <v>18.6</v>
       </c>
       <c r="R27" s="2">
         <v>26537</v>
@@ -1393,14 +1432,23 @@
       <c r="C28">
         <v>27</v>
       </c>
+      <c r="D28">
+        <v>26.8</v>
+      </c>
+      <c r="E28">
+        <v>18.2</v>
+      </c>
+      <c r="F28">
+        <v>22.5</v>
+      </c>
       <c r="H28">
         <v>19.2</v>
       </c>
-      <c r="J28">
-        <v>20.8</v>
-      </c>
       <c r="K28">
-        <v>17.4</v>
+        <v>16.5</v>
+      </c>
+      <c r="M28">
+        <v>18.6</v>
       </c>
       <c r="R28" s="2">
         <v>26538</v>
@@ -1422,20 +1470,11 @@
       <c r="C29">
         <v>28</v>
       </c>
-      <c r="D29">
-        <v>25.4</v>
-      </c>
-      <c r="E29">
-        <v>18.8</v>
-      </c>
-      <c r="F29">
-        <v>22.1</v>
-      </c>
       <c r="H29">
         <v>19.4</v>
       </c>
-      <c r="J29">
-        <v>19.6</v>
+      <c r="M29">
+        <v>16.8</v>
       </c>
       <c r="R29" s="2">
         <v>26539</v>
@@ -1458,10 +1497,19 @@
         <v>29</v>
       </c>
       <c r="H30">
-        <v>17.4</v>
-      </c>
-      <c r="J30">
-        <v>26.4</v>
+        <v>17.5</v>
+      </c>
+      <c r="I30">
+        <v>28.6</v>
+      </c>
+      <c r="K30">
+        <v>15</v>
+      </c>
+      <c r="L30">
+        <v>17.8</v>
+      </c>
+      <c r="M30">
+        <v>20</v>
       </c>
       <c r="R30" s="2">
         <v>26540</v>
@@ -1486,11 +1534,8 @@
       <c r="H31">
         <v>16.4</v>
       </c>
-      <c r="J31">
-        <v>26.4</v>
-      </c>
       <c r="M31">
-        <v>17.2</v>
+        <v>20</v>
       </c>
       <c r="R31" s="2">
         <v>26541</v>
@@ -1515,8 +1560,8 @@
       <c r="H32">
         <v>18.8</v>
       </c>
-      <c r="J32">
-        <v>26.4</v>
+      <c r="M32">
+        <v>20.6</v>
       </c>
       <c r="R32" s="2">
         <v>26542</v>

--- a/results/04_final_refined_daily_hydroclimate_data/904/Daily_temperature_and_precipitation_station_904.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/904/Daily_temperature_and_precipitation_station_904.xlsx
@@ -514,10 +514,10 @@
         <v>1</v>
       </c>
       <c r="D2">
-        <v>28.2</v>
+        <v>27.6</v>
       </c>
       <c r="E2">
-        <v>17.5</v>
+        <v>17.6</v>
       </c>
       <c r="F2">
         <v>23</v>
@@ -525,6 +525,12 @@
       <c r="G2">
         <v>18.6</v>
       </c>
+      <c r="H2">
+        <v>18.6</v>
+      </c>
+      <c r="K2">
+        <v>16.8</v>
+      </c>
       <c r="R2" s="2">
         <v>26512</v>
       </c>
@@ -557,9 +563,15 @@
       <c r="G3">
         <v>0</v>
       </c>
+      <c r="H3">
+        <v>17.6</v>
+      </c>
       <c r="J3">
         <v>24.8</v>
       </c>
+      <c r="K3">
+        <v>15.8</v>
+      </c>
       <c r="M3">
         <v>15.7</v>
       </c>
@@ -595,9 +607,15 @@
       <c r="G4">
         <v>0</v>
       </c>
+      <c r="H4">
+        <v>18.4</v>
+      </c>
       <c r="J4">
         <v>24.6</v>
       </c>
+      <c r="K4">
+        <v>16</v>
+      </c>
       <c r="M4">
         <v>18.1</v>
       </c>
@@ -633,11 +651,17 @@
       <c r="G5">
         <v>0</v>
       </c>
+      <c r="H5">
+        <v>18.6</v>
+      </c>
       <c r="J5">
         <v>25.8</v>
       </c>
+      <c r="K5">
+        <v>17.4</v>
+      </c>
       <c r="M5">
-        <v>19.6</v>
+        <v>16.9</v>
       </c>
       <c r="R5" s="2">
         <v>26515</v>
@@ -660,20 +684,26 @@
         <v>5</v>
       </c>
       <c r="D6">
-        <v>29.9</v>
+        <v>30.5</v>
       </c>
       <c r="E6">
-        <v>17.3</v>
+        <v>17.2</v>
       </c>
       <c r="F6">
-        <v>23.59</v>
+        <v>23.9</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
+      <c r="H6">
+        <v>18.5</v>
+      </c>
       <c r="J6">
         <v>26.2</v>
       </c>
+      <c r="K6">
+        <v>16.4</v>
+      </c>
       <c r="M6">
         <v>19.8</v>
       </c>
@@ -709,8 +739,11 @@
       <c r="H7">
         <v>18.4</v>
       </c>
+      <c r="I7">
+        <v>28.4</v>
+      </c>
       <c r="K7">
-        <v>18.2</v>
+        <v>17.2</v>
       </c>
       <c r="L7">
         <v>20</v>
@@ -747,6 +780,9 @@
       <c r="H8">
         <v>18.6</v>
       </c>
+      <c r="I8">
+        <v>28.2</v>
+      </c>
       <c r="K8">
         <v>17.4</v>
       </c>
@@ -785,6 +821,9 @@
       <c r="H9">
         <v>17.6</v>
       </c>
+      <c r="I9">
+        <v>26</v>
+      </c>
       <c r="K9">
         <v>15.8</v>
       </c>
@@ -823,6 +862,9 @@
       <c r="H10">
         <v>19.8</v>
       </c>
+      <c r="I10">
+        <v>26.8</v>
+      </c>
       <c r="K10">
         <v>16.8</v>
       </c>
@@ -853,14 +895,17 @@
         <v>28.8</v>
       </c>
       <c r="E11">
-        <v>17.8</v>
+        <v>18.8</v>
       </c>
       <c r="F11">
-        <v>23.3</v>
+        <v>23.8</v>
       </c>
       <c r="H11">
         <v>18.6</v>
       </c>
+      <c r="I11">
+        <v>28.8</v>
+      </c>
       <c r="K11">
         <v>15.9</v>
       </c>
@@ -888,14 +933,17 @@
         <v>11</v>
       </c>
       <c r="D12">
-        <v>30.3</v>
+        <v>30.4</v>
       </c>
       <c r="E12">
-        <v>17.9</v>
+        <v>17.8</v>
       </c>
       <c r="F12">
         <v>24.1</v>
       </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
       <c r="K12">
         <v>16.2</v>
       </c>
@@ -928,11 +976,17 @@
       <c r="F13">
         <v>23.7</v>
       </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>18.6</v>
+      </c>
       <c r="I13">
         <v>29.6</v>
       </c>
       <c r="K13">
-        <v>17.2</v>
+        <v>16.5</v>
       </c>
       <c r="L13">
         <v>17</v>
@@ -966,15 +1020,27 @@
       <c r="F14">
         <v>24.4</v>
       </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>18.8</v>
+      </c>
       <c r="I14">
         <v>30.6</v>
       </c>
+      <c r="J14">
+        <v>26.4</v>
+      </c>
       <c r="K14">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="L14">
         <v>18.2</v>
       </c>
+      <c r="M14">
+        <v>17.5</v>
+      </c>
       <c r="R14" s="2">
         <v>26524</v>
       </c>
@@ -1004,8 +1070,26 @@
       <c r="F15">
         <v>22.3</v>
       </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>18.8</v>
+      </c>
+      <c r="I15">
+        <v>26.5</v>
+      </c>
+      <c r="J15">
+        <v>24.4</v>
+      </c>
       <c r="K15">
-        <v>17.4</v>
+        <v>16.7</v>
+      </c>
+      <c r="L15">
+        <v>17.1</v>
+      </c>
+      <c r="M15">
+        <v>15.9</v>
       </c>
       <c r="R15" s="2">
         <v>26525</v>
@@ -1036,6 +1120,9 @@
       <c r="F16">
         <v>23</v>
       </c>
+      <c r="G16">
+        <v>6.8</v>
+      </c>
       <c r="I16">
         <v>23.2</v>
       </c>
@@ -1069,14 +1156,20 @@
         <v>22.8</v>
       </c>
       <c r="E17">
-        <v>16</v>
-      </c>
-      <c r="F17">
-        <v>19.4</v>
+        <v>15.6</v>
+      </c>
+      <c r="J17">
+        <v>19.8</v>
+      </c>
+      <c r="K17">
+        <v>15.8</v>
       </c>
       <c r="L17">
         <v>19.4</v>
       </c>
+      <c r="P17" t="s">
+        <v>20</v>
+      </c>
       <c r="R17" s="2">
         <v>26527</v>
       </c>
@@ -1106,9 +1199,21 @@
       <c r="F18">
         <v>23</v>
       </c>
+      <c r="H18">
+        <v>18.4</v>
+      </c>
+      <c r="J18">
+        <v>24.4</v>
+      </c>
+      <c r="K18">
+        <v>16</v>
+      </c>
       <c r="L18">
         <v>21.2</v>
       </c>
+      <c r="M18">
+        <v>15.9</v>
+      </c>
       <c r="R18" s="2">
         <v>26528</v>
       </c>
@@ -1141,6 +1246,12 @@
       <c r="I19">
         <v>27.4</v>
       </c>
+      <c r="J19">
+        <v>24.8</v>
+      </c>
+      <c r="K19">
+        <v>16.8</v>
+      </c>
       <c r="L19">
         <v>18.1</v>
       </c>
@@ -1168,10 +1279,10 @@
         <v>27.4</v>
       </c>
       <c r="E20">
-        <v>18.2</v>
+        <v>18</v>
       </c>
       <c r="F20">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="H20">
         <v>18.4</v>
@@ -1179,6 +1290,9 @@
       <c r="I20">
         <v>27.4</v>
       </c>
+      <c r="J20">
+        <v>25.6</v>
+      </c>
       <c r="K20">
         <v>15.7</v>
       </c>
@@ -1209,22 +1323,22 @@
         <v>26.8</v>
       </c>
       <c r="E21">
-        <v>15.9</v>
+        <v>17.4</v>
       </c>
       <c r="F21">
-        <v>21.4</v>
+        <v>22.1</v>
       </c>
       <c r="H21">
         <v>18.6</v>
       </c>
-      <c r="I21">
-        <v>25.6</v>
+      <c r="J21">
+        <v>23.6</v>
       </c>
       <c r="K21">
         <v>16.8</v>
       </c>
       <c r="L21">
-        <v>17.2</v>
+        <v>19.8</v>
       </c>
       <c r="R21" s="2">
         <v>26531</v>
@@ -1249,14 +1363,20 @@
       <c r="D22">
         <v>26.2</v>
       </c>
+      <c r="E22">
+        <v>17.6</v>
+      </c>
       <c r="F22">
-        <v>19.9</v>
+        <v>21.9</v>
+      </c>
+      <c r="G22">
+        <v>7.2</v>
       </c>
       <c r="H22">
         <v>18.4</v>
       </c>
-      <c r="O22" t="s">
-        <v>20</v>
+      <c r="K22">
+        <v>16.8</v>
       </c>
       <c r="R22" s="2">
         <v>26532</v>
@@ -1287,15 +1407,27 @@
       <c r="F23">
         <v>21.9</v>
       </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
       <c r="H23">
         <v>17.4</v>
       </c>
+      <c r="I23">
+        <v>26.6</v>
+      </c>
       <c r="J23">
         <v>21.8</v>
       </c>
       <c r="K23">
         <v>14.7</v>
       </c>
+      <c r="L23">
+        <v>17.1</v>
+      </c>
+      <c r="M23">
+        <v>17.2</v>
+      </c>
       <c r="R23" s="2">
         <v>26533</v>
       </c>
@@ -1316,12 +1448,36 @@
       <c r="C24">
         <v>23</v>
       </c>
+      <c r="D24">
+        <v>28.2</v>
+      </c>
+      <c r="E24">
+        <v>18</v>
+      </c>
+      <c r="F24">
+        <v>23.1</v>
+      </c>
+      <c r="G24">
+        <v>10</v>
+      </c>
       <c r="H24">
         <v>18.4</v>
       </c>
+      <c r="I24">
+        <v>28.2</v>
+      </c>
       <c r="J24">
         <v>24.6</v>
       </c>
+      <c r="K24">
+        <v>17.2</v>
+      </c>
+      <c r="L24">
+        <v>19</v>
+      </c>
+      <c r="M24">
+        <v>18.1</v>
+      </c>
       <c r="R24" s="2">
         <v>26534</v>
       </c>
@@ -1342,12 +1498,36 @@
       <c r="C25">
         <v>24</v>
       </c>
+      <c r="D25">
+        <v>24.2</v>
+      </c>
+      <c r="E25">
+        <v>17.6</v>
+      </c>
+      <c r="F25">
+        <v>20.9</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
       <c r="H25">
-        <v>17.9</v>
+        <v>17.6</v>
+      </c>
+      <c r="I25">
+        <v>24.2</v>
       </c>
       <c r="J25">
         <v>20.4</v>
       </c>
+      <c r="K25">
+        <v>15.8</v>
+      </c>
+      <c r="L25">
+        <v>16.6</v>
+      </c>
+      <c r="M25">
+        <v>18.1</v>
+      </c>
       <c r="R25" s="2">
         <v>26535</v>
       </c>
@@ -1377,8 +1557,14 @@
       <c r="F26">
         <v>23.2</v>
       </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
       <c r="H26">
-        <v>18.7</v>
+        <v>18.6</v>
+      </c>
+      <c r="I26">
+        <v>28.6</v>
       </c>
       <c r="J26">
         <v>20.4</v>
@@ -1386,6 +1572,9 @@
       <c r="K26">
         <v>16.5</v>
       </c>
+      <c r="L26">
+        <v>19.1</v>
+      </c>
       <c r="R26" s="2">
         <v>26536</v>
       </c>
@@ -1406,9 +1595,30 @@
       <c r="C27">
         <v>26</v>
       </c>
+      <c r="D27">
+        <v>26.6</v>
+      </c>
+      <c r="E27">
+        <v>18.6</v>
+      </c>
+      <c r="F27">
+        <v>22.6</v>
+      </c>
+      <c r="G27">
+        <v>3.6</v>
+      </c>
       <c r="H27">
         <v>19.4</v>
       </c>
+      <c r="I27">
+        <v>46.65</v>
+      </c>
+      <c r="K27">
+        <v>17.6</v>
+      </c>
+      <c r="L27">
+        <v>20.48</v>
+      </c>
       <c r="M27">
         <v>18.6</v>
       </c>
@@ -1433,20 +1643,29 @@
         <v>27</v>
       </c>
       <c r="D28">
-        <v>26.8</v>
+        <v>26.2</v>
       </c>
       <c r="E28">
-        <v>18.2</v>
+        <v>18.4</v>
       </c>
       <c r="F28">
-        <v>22.5</v>
+        <v>22.2</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
       </c>
       <c r="H28">
         <v>19.2</v>
       </c>
+      <c r="I28">
+        <v>26.2</v>
+      </c>
       <c r="K28">
         <v>16.5</v>
       </c>
+      <c r="L28">
+        <v>20</v>
+      </c>
       <c r="M28">
         <v>18.6</v>
       </c>
@@ -1470,9 +1689,30 @@
       <c r="C29">
         <v>28</v>
       </c>
+      <c r="D29">
+        <v>25.4</v>
+      </c>
+      <c r="E29">
+        <v>18.4</v>
+      </c>
+      <c r="F29">
+        <v>21.9</v>
+      </c>
+      <c r="G29">
+        <v>5.8</v>
+      </c>
       <c r="H29">
         <v>19.4</v>
       </c>
+      <c r="I29">
+        <v>22.6</v>
+      </c>
+      <c r="K29">
+        <v>17.2</v>
+      </c>
+      <c r="L29">
+        <v>15.1</v>
+      </c>
       <c r="M29">
         <v>16.8</v>
       </c>
@@ -1496,6 +1736,18 @@
       <c r="C30">
         <v>29</v>
       </c>
+      <c r="D30">
+        <v>29</v>
+      </c>
+      <c r="E30">
+        <v>16</v>
+      </c>
+      <c r="F30">
+        <v>22.5</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
       <c r="H30">
         <v>17.5</v>
       </c>
@@ -1531,9 +1783,30 @@
       <c r="C31">
         <v>30</v>
       </c>
+      <c r="D31">
+        <v>30.4</v>
+      </c>
+      <c r="E31">
+        <v>15</v>
+      </c>
+      <c r="F31">
+        <v>22.7</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
       <c r="H31">
         <v>16.4</v>
       </c>
+      <c r="I31">
+        <v>20.4</v>
+      </c>
+      <c r="K31">
+        <v>14.8</v>
+      </c>
+      <c r="L31">
+        <v>20.6</v>
+      </c>
       <c r="M31">
         <v>20</v>
       </c>
@@ -1557,11 +1830,32 @@
       <c r="C32">
         <v>31</v>
       </c>
+      <c r="D32">
+        <v>27.6</v>
+      </c>
+      <c r="E32">
+        <v>16.4</v>
+      </c>
+      <c r="F32">
+        <v>22</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
       <c r="H32">
         <v>18.8</v>
       </c>
+      <c r="I32">
+        <v>20.6</v>
+      </c>
+      <c r="K32">
+        <v>15.6</v>
+      </c>
+      <c r="L32">
+        <v>21.8</v>
+      </c>
       <c r="M32">
-        <v>20.6</v>
+        <v>20</v>
       </c>
       <c r="R32" s="2">
         <v>26542</v>

--- a/results/04_final_refined_daily_hydroclimate_data/904/Daily_temperature_and_precipitation_station_904.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/904/Daily_temperature_and_precipitation_station_904.xlsx
@@ -736,6 +736,9 @@
       <c r="F7">
         <v>22.6</v>
       </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
       <c r="H7">
         <v>18.4</v>
       </c>
@@ -777,6 +780,9 @@
       <c r="F8">
         <v>23.1</v>
       </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
       <c r="H8">
         <v>18.6</v>
       </c>
@@ -818,6 +824,9 @@
       <c r="F9">
         <v>21.6</v>
       </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
       <c r="H9">
         <v>17.6</v>
       </c>
@@ -859,6 +868,9 @@
       <c r="F10">
         <v>23.3</v>
       </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
       <c r="H10">
         <v>19.8</v>
       </c>
@@ -895,10 +907,13 @@
         <v>28.8</v>
       </c>
       <c r="E11">
-        <v>18.8</v>
+        <v>18.4</v>
       </c>
       <c r="F11">
-        <v>23.8</v>
+        <v>23.6</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
       </c>
       <c r="H11">
         <v>18.6</v>
@@ -968,7 +983,7 @@
         <v>12</v>
       </c>
       <c r="D13">
-        <v>29.6</v>
+        <v>29.8</v>
       </c>
       <c r="E13">
         <v>17.8</v>
@@ -1077,7 +1092,7 @@
         <v>18.8</v>
       </c>
       <c r="I15">
-        <v>26.5</v>
+        <v>26.6</v>
       </c>
       <c r="J15">
         <v>24.4</v>
@@ -1238,10 +1253,10 @@
         <v>27.4</v>
       </c>
       <c r="E19">
-        <v>18.2</v>
+        <v>17.2</v>
       </c>
       <c r="F19">
-        <v>22.8</v>
+        <v>22.3</v>
       </c>
       <c r="I19">
         <v>27.4</v>
@@ -1413,18 +1428,12 @@
       <c r="H23">
         <v>17.4</v>
       </c>
-      <c r="I23">
-        <v>26.6</v>
-      </c>
       <c r="J23">
         <v>21.8</v>
       </c>
       <c r="K23">
         <v>14.7</v>
       </c>
-      <c r="L23">
-        <v>17.1</v>
-      </c>
       <c r="M23">
         <v>17.2</v>
       </c>
@@ -1610,9 +1619,6 @@
       <c r="H27">
         <v>19.4</v>
       </c>
-      <c r="I27">
-        <v>46.65</v>
-      </c>
       <c r="K27">
         <v>17.6</v>
       </c>
@@ -1643,13 +1649,13 @@
         <v>27</v>
       </c>
       <c r="D28">
-        <v>26.2</v>
+        <v>26</v>
       </c>
       <c r="E28">
-        <v>18.4</v>
+        <v>18.2</v>
       </c>
       <c r="F28">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -1657,9 +1663,6 @@
       <c r="H28">
         <v>19.2</v>
       </c>
-      <c r="I28">
-        <v>26.2</v>
-      </c>
       <c r="K28">
         <v>16.5</v>
       </c>
@@ -1737,19 +1740,19 @@
         <v>29</v>
       </c>
       <c r="D30">
-        <v>29</v>
+        <v>28.4</v>
       </c>
       <c r="E30">
         <v>16</v>
       </c>
       <c r="F30">
-        <v>22.5</v>
+        <v>22.3</v>
       </c>
       <c r="G30">
         <v>0</v>
       </c>
       <c r="H30">
-        <v>17.5</v>
+        <v>17.4</v>
       </c>
       <c r="I30">
         <v>28.6</v>
@@ -1784,10 +1787,10 @@
         <v>30</v>
       </c>
       <c r="D31">
-        <v>30.4</v>
+        <v>30.6</v>
       </c>
       <c r="E31">
-        <v>15</v>
+        <v>15.2</v>
       </c>
       <c r="F31">
         <v>22.7</v>
@@ -1799,13 +1802,13 @@
         <v>16.4</v>
       </c>
       <c r="I31">
-        <v>20.4</v>
+        <v>30.4</v>
       </c>
       <c r="K31">
         <v>14.8</v>
       </c>
       <c r="L31">
-        <v>20.6</v>
+        <v>16.3</v>
       </c>
       <c r="M31">
         <v>20</v>
@@ -1831,22 +1834,19 @@
         <v>31</v>
       </c>
       <c r="D32">
-        <v>27.6</v>
+        <v>33.6</v>
       </c>
       <c r="E32">
         <v>16.4</v>
       </c>
       <c r="F32">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G32">
         <v>0</v>
       </c>
       <c r="H32">
         <v>18.8</v>
-      </c>
-      <c r="I32">
-        <v>20.6</v>
       </c>
       <c r="K32">
         <v>15.6</v>

--- a/results/04_final_refined_daily_hydroclimate_data/904/Daily_temperature_and_precipitation_station_904.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/904/Daily_temperature_and_precipitation_station_904.xlsx
@@ -907,10 +907,10 @@
         <v>28.8</v>
       </c>
       <c r="E11">
-        <v>18.4</v>
+        <v>18.8</v>
       </c>
       <c r="F11">
-        <v>23.6</v>
+        <v>23.8</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1428,12 +1428,18 @@
       <c r="H23">
         <v>17.4</v>
       </c>
+      <c r="I23">
+        <v>26.6</v>
+      </c>
       <c r="J23">
         <v>21.8</v>
       </c>
       <c r="K23">
         <v>14.7</v>
       </c>
+      <c r="L23">
+        <v>17.1</v>
+      </c>
       <c r="M23">
         <v>17.2</v>
       </c>
@@ -1625,9 +1631,6 @@
       <c r="L27">
         <v>20.48</v>
       </c>
-      <c r="M27">
-        <v>18.6</v>
-      </c>
       <c r="R27" s="2">
         <v>26537</v>
       </c>
@@ -1649,10 +1652,10 @@
         <v>27</v>
       </c>
       <c r="D28">
-        <v>26</v>
+        <v>26.2</v>
       </c>
       <c r="E28">
-        <v>18.2</v>
+        <v>18.4</v>
       </c>
       <c r="F28">
         <v>22.3</v>
@@ -1663,14 +1666,14 @@
       <c r="H28">
         <v>19.2</v>
       </c>
+      <c r="I28">
+        <v>26.2</v>
+      </c>
       <c r="K28">
         <v>16.5</v>
       </c>
       <c r="L28">
-        <v>20</v>
-      </c>
-      <c r="M28">
-        <v>18.6</v>
+        <v>17.3</v>
       </c>
       <c r="R28" s="2">
         <v>26538</v>
@@ -1707,17 +1710,11 @@
       <c r="H29">
         <v>19.4</v>
       </c>
-      <c r="I29">
-        <v>22.6</v>
-      </c>
       <c r="K29">
         <v>17.2</v>
       </c>
       <c r="L29">
-        <v>15.1</v>
-      </c>
-      <c r="M29">
-        <v>16.8</v>
+        <v>17.6</v>
       </c>
       <c r="R29" s="2">
         <v>26539</v>
@@ -1763,9 +1760,6 @@
       <c r="L30">
         <v>17.8</v>
       </c>
-      <c r="M30">
-        <v>20</v>
-      </c>
       <c r="R30" s="2">
         <v>26540</v>
       </c>
@@ -1810,9 +1804,6 @@
       <c r="L31">
         <v>16.3</v>
       </c>
-      <c r="M31">
-        <v>20</v>
-      </c>
       <c r="R31" s="2">
         <v>26541</v>
       </c>
@@ -1853,9 +1844,6 @@
       </c>
       <c r="L32">
         <v>21.8</v>
-      </c>
-      <c r="M32">
-        <v>20</v>
       </c>
       <c r="R32" s="2">
         <v>26542</v>

--- a/results/04_final_refined_daily_hydroclimate_data/904/Daily_temperature_and_precipitation_station_904.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/904/Daily_temperature_and_precipitation_station_904.xlsx
@@ -573,7 +573,7 @@
         <v>15.8</v>
       </c>
       <c r="M3">
-        <v>15.7</v>
+        <v>18.6</v>
       </c>
       <c r="R3" s="2">
         <v>26513</v>
@@ -614,10 +614,10 @@
         <v>24.6</v>
       </c>
       <c r="K4">
-        <v>16</v>
+        <v>16.8</v>
       </c>
       <c r="M4">
-        <v>18.1</v>
+        <v>20</v>
       </c>
       <c r="R4" s="2">
         <v>26514</v>
@@ -661,7 +661,7 @@
         <v>17.4</v>
       </c>
       <c r="M5">
-        <v>16.9</v>
+        <v>19.6</v>
       </c>
       <c r="R5" s="2">
         <v>26515</v>
@@ -922,7 +922,7 @@
         <v>28.8</v>
       </c>
       <c r="K11">
-        <v>15.9</v>
+        <v>16.8</v>
       </c>
       <c r="L11">
         <v>21.2</v>
@@ -1001,10 +1001,7 @@
         <v>29.6</v>
       </c>
       <c r="K13">
-        <v>16.5</v>
-      </c>
-      <c r="L13">
-        <v>17</v>
+        <v>17.2</v>
       </c>
       <c r="R13" s="2">
         <v>26523</v>
@@ -1048,13 +1045,7 @@
         <v>26.4</v>
       </c>
       <c r="K14">
-        <v>16.7</v>
-      </c>
-      <c r="L14">
-        <v>18.2</v>
-      </c>
-      <c r="M14">
-        <v>17.5</v>
+        <v>17.4</v>
       </c>
       <c r="R14" s="2">
         <v>26524</v>
@@ -1098,13 +1089,7 @@
         <v>24.4</v>
       </c>
       <c r="K15">
-        <v>16.7</v>
-      </c>
-      <c r="L15">
-        <v>17.1</v>
-      </c>
-      <c r="M15">
-        <v>15.9</v>
+        <v>17.4</v>
       </c>
       <c r="R15" s="2">
         <v>26525</v>
@@ -1138,15 +1123,15 @@
       <c r="G16">
         <v>6.8</v>
       </c>
+      <c r="H16">
+        <v>18.2</v>
+      </c>
       <c r="I16">
         <v>23.2</v>
       </c>
       <c r="K16">
         <v>16.8</v>
       </c>
-      <c r="L16">
-        <v>17.1</v>
-      </c>
       <c r="R16" s="2">
         <v>26526</v>
       </c>
@@ -1221,14 +1206,11 @@
         <v>24.4</v>
       </c>
       <c r="K18">
-        <v>16</v>
+        <v>16.8</v>
       </c>
       <c r="L18">
         <v>21.2</v>
       </c>
-      <c r="M18">
-        <v>15.9</v>
-      </c>
       <c r="R18" s="2">
         <v>26528</v>
       </c>
@@ -1258,6 +1240,9 @@
       <c r="F19">
         <v>22.3</v>
       </c>
+      <c r="H19">
+        <v>18.4</v>
+      </c>
       <c r="I19">
         <v>27.4</v>
       </c>
@@ -1268,7 +1253,7 @@
         <v>16.8</v>
       </c>
       <c r="L19">
-        <v>18.1</v>
+        <v>20.8</v>
       </c>
       <c r="R19" s="2">
         <v>26529</v>
@@ -1309,10 +1294,10 @@
         <v>25.6</v>
       </c>
       <c r="K20">
-        <v>15.7</v>
+        <v>16.6</v>
       </c>
       <c r="L20">
-        <v>18.1</v>
+        <v>20.8</v>
       </c>
       <c r="R20" s="2">
         <v>26530</v>
@@ -1350,7 +1335,7 @@
         <v>23.6</v>
       </c>
       <c r="K21">
-        <v>16.8</v>
+        <v>17.4</v>
       </c>
       <c r="L21">
         <v>19.8</v>
@@ -1435,13 +1420,7 @@
         <v>21.8</v>
       </c>
       <c r="K23">
-        <v>14.7</v>
-      </c>
-      <c r="L23">
-        <v>17.1</v>
-      </c>
-      <c r="M23">
-        <v>17.2</v>
+        <v>15.6</v>
       </c>
       <c r="R23" s="2">
         <v>26533</v>
@@ -1487,12 +1466,6 @@
       <c r="K24">
         <v>17.2</v>
       </c>
-      <c r="L24">
-        <v>19</v>
-      </c>
-      <c r="M24">
-        <v>18.1</v>
-      </c>
       <c r="R24" s="2">
         <v>26534</v>
       </c>
@@ -1537,11 +1510,8 @@
       <c r="K25">
         <v>15.8</v>
       </c>
-      <c r="L25">
-        <v>16.6</v>
-      </c>
       <c r="M25">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="R25" s="2">
         <v>26535</v>
@@ -1585,10 +1555,7 @@
         <v>20.4</v>
       </c>
       <c r="K26">
-        <v>16.5</v>
-      </c>
-      <c r="L26">
-        <v>19.1</v>
+        <v>17.2</v>
       </c>
       <c r="R26" s="2">
         <v>26536</v>
@@ -1670,10 +1637,10 @@
         <v>26.2</v>
       </c>
       <c r="K28">
-        <v>16.5</v>
+        <v>17.4</v>
       </c>
       <c r="L28">
-        <v>17.3</v>
+        <v>20</v>
       </c>
       <c r="R28" s="2">
         <v>26538</v>
@@ -1755,10 +1722,10 @@
         <v>28.6</v>
       </c>
       <c r="K30">
-        <v>15</v>
+        <v>15.8</v>
       </c>
       <c r="L30">
-        <v>17.8</v>
+        <v>21</v>
       </c>
       <c r="R30" s="2">
         <v>26540</v>
@@ -1802,7 +1769,7 @@
         <v>14.8</v>
       </c>
       <c r="L31">
-        <v>16.3</v>
+        <v>20.6</v>
       </c>
       <c r="R31" s="2">
         <v>26541</v>
